--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -521,10 +521,10 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>4.526479999999951</v>
+        <v>4.52647999999995</v>
       </c>
       <c r="C6">
-        <v>4.666221474017745</v>
+        <v>4.666221474017744</v>
       </c>
       <c r="D6">
         <v>2.919999999999996</v>
@@ -550,7 +550,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.905332478545524</v>
+        <v>2.905332478545528</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.105200000000003</v>
+        <v>6.105200000000004</v>
       </c>
       <c r="C8">
-        <v>6.287706569606076</v>
+        <v>6.287706569606078</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.928560000000143</v>
+        <v>2.928560000000144</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.105200000000004</v>
+        <v>6.105200000000005</v>
       </c>
       <c r="C8">
         <v>6.287706569606078</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -43,10 +43,10 @@
     <t>NestedSelected</t>
   </si>
   <si>
+    <t>ExtraTrees</t>
+  </si>
+  <si>
     <t>Ridge</t>
-  </si>
-  <si>
-    <t>ExtraTrees</t>
   </si>
   <si>
     <t>TreeEnsemble</t>
@@ -501,16 +501,16 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>3.268073854662842</v>
+        <v>4.355919999999944</v>
       </c>
       <c r="C5">
-        <v>3.358999240744585</v>
+        <v>4.496165686640881</v>
       </c>
       <c r="D5">
         <v>2.919999999999996</v>
       </c>
       <c r="E5">
-        <v>2.956940250134659</v>
+        <v>2.871280000000134</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -521,16 +521,16 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>4.52647999999995</v>
+        <v>4.470765686781189</v>
       </c>
       <c r="C6">
-        <v>4.666221474017744</v>
+        <v>4.60907945471731</v>
       </c>
       <c r="D6">
         <v>2.919999999999996</v>
       </c>
       <c r="E6">
-        <v>2.878160000000127</v>
+        <v>3.013076430967813</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>5.27358357792292</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="C7">
-        <v>5.432665386242507</v>
+        <v>5.080454467018148</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.905332478545528</v>
+        <v>2.898677190011187</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.105200000000005</v>
+        <v>5.717839999999996</v>
       </c>
       <c r="C8">
-        <v>6.287706569606078</v>
+        <v>5.888339112555603</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.928560000000144</v>
+        <v>2.916560000000142</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -550,7 +550,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011187</v>
+        <v>2.898677190011192</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -550,7 +550,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011192</v>
+        <v>2.898677190011187</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626762</v>
       </c>
       <c r="C7">
-        <v>5.080454467018148</v>
+        <v>5.080454467018146</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011187</v>
+        <v>2.898677190011191</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626762</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="C7">
-        <v>5.080454467018146</v>
+        <v>5.080454467018148</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011191</v>
+        <v>2.898677190011192</v>
       </c>
       <c r="F7">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626763</v>
       </c>
       <c r="C7">
-        <v>5.080454467018148</v>
+        <v>5.080454467018147</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011192</v>
+        <v>2.898677190011188</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999996</v>
+        <v>5.717839999999995</v>
       </c>
       <c r="C8">
-        <v>5.888339112555603</v>
+        <v>5.888339112555601</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000142</v>
+        <v>2.916560000000145</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626763</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="C7">
-        <v>5.080454467018147</v>
+        <v>5.080454467018148</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011188</v>
+        <v>2.898677190011192</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999995</v>
+        <v>5.717839999999996</v>
       </c>
       <c r="C8">
-        <v>5.888339112555601</v>
+        <v>5.888339112555603</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000145</v>
+        <v>2.916560000000142</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,10 +541,10 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626763</v>
       </c>
       <c r="C7">
-        <v>5.080454467018148</v>
+        <v>5.080454467018147</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999996</v>
+        <v>5.717839999999995</v>
       </c>
       <c r="C8">
-        <v>5.888339112555603</v>
+        <v>5.888339112555601</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000142</v>
+        <v>2.916560000000145</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626763</v>
+        <v>4.927364392626759</v>
       </c>
       <c r="C7">
-        <v>5.080454467018147</v>
+        <v>5.080454467018144</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011192</v>
+        <v>2.898677190011186</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999995</v>
+        <v>5.717839999999993</v>
       </c>
       <c r="C8">
         <v>5.888339112555601</v>
@@ -570,7 +570,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000145</v>
+        <v>2.916560000000143</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626759</v>
+        <v>4.92736439262676</v>
       </c>
       <c r="C7">
-        <v>5.080454467018144</v>
+        <v>5.080454467018145</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011186</v>
+        <v>2.898677190011185</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999993</v>
+        <v>5.717839999999994</v>
       </c>
       <c r="C8">
         <v>5.888339112555601</v>
@@ -570,7 +570,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000143</v>
+        <v>2.916560000000146</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.92736439262676</v>
+        <v>4.927364392626764</v>
       </c>
       <c r="C7">
-        <v>5.080454467018145</v>
+        <v>5.080454467018148</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011185</v>
+        <v>2.898677190011187</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>5.717839999999994</v>
+        <v>5.717839999999996</v>
       </c>
       <c r="C8">
-        <v>5.888339112555601</v>
+        <v>5.888339112555603</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.916560000000146</v>
+        <v>2.916560000000142</v>
       </c>
       <c r="F8">
         <v>5</v>

--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>4.927364392626764</v>
+        <v>4.927364392626762</v>
       </c>
       <c r="C7">
-        <v>5.080454467018148</v>
+        <v>5.080454467018146</v>
       </c>
       <c r="D7">
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.898677190011192</v>
+        <v>2.898677190011194</v>
       </c>
       <c r="F7">
         <v>5</v>
